--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/26.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/26.xlsx
@@ -426,13 +426,13 @@
         <v>-26.01802749821644</v>
       </c>
       <c r="E2">
-        <v>-17.82217381181491</v>
+        <v>-17.97550341324062</v>
       </c>
       <c r="F2">
-        <v>-1.078826091018249</v>
+        <v>-0.904064591682235</v>
       </c>
       <c r="G2">
-        <v>-11.66104027383285</v>
+        <v>-11.11797507302526</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-26.34125621619176</v>
       </c>
       <c r="E3">
-        <v>-17.78936501762934</v>
+        <v>-17.6689030805513</v>
       </c>
       <c r="F3">
-        <v>-0.9538047407507341</v>
+        <v>-1.081671533046866</v>
       </c>
       <c r="G3">
-        <v>-11.69638696855565</v>
+        <v>-11.56498810555643</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-26.57594752377432</v>
       </c>
       <c r="E4">
-        <v>-18.72815390721146</v>
+        <v>-19.08302324434854</v>
       </c>
       <c r="F4">
-        <v>-0.572947916700411</v>
+        <v>-0.5621973645468791</v>
       </c>
       <c r="G4">
-        <v>-11.31135728015625</v>
+        <v>-11.15255703172849</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-26.6515859117011</v>
       </c>
       <c r="E5">
-        <v>-19.05326211317013</v>
+        <v>-19.52885151040369</v>
       </c>
       <c r="F5">
-        <v>-0.8612263998138614</v>
+        <v>-0.835074840907481</v>
       </c>
       <c r="G5">
-        <v>-11.65438276675338</v>
+        <v>-10.87161751617486</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-26.54990341215698</v>
       </c>
       <c r="E6">
-        <v>-19.75852665512472</v>
+        <v>-19.73479745132452</v>
       </c>
       <c r="F6">
-        <v>-0.5959657617220009</v>
+        <v>-0.9478603762682448</v>
       </c>
       <c r="G6">
-        <v>-11.38656625371741</v>
+        <v>-10.58785079473069</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-26.25997615886828</v>
       </c>
       <c r="E7">
-        <v>-21.15180678153866</v>
+        <v>-20.56493013556661</v>
       </c>
       <c r="F7">
-        <v>-0.5388266350116966</v>
+        <v>-0.7229710519192211</v>
       </c>
       <c r="G7">
-        <v>-11.19128710399242</v>
+        <v>-10.70862280654884</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-25.77751017779322</v>
       </c>
       <c r="E8">
-        <v>-21.22919387385574</v>
+        <v>-21.42893127691206</v>
       </c>
       <c r="F8">
-        <v>-0.5898797464136329</v>
+        <v>-0.7544332742449491</v>
       </c>
       <c r="G8">
-        <v>-11.22536917031922</v>
+        <v>-10.22357491631699</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-25.10127578586373</v>
       </c>
       <c r="E9">
-        <v>-21.86695698225198</v>
+        <v>-21.94023674864411</v>
       </c>
       <c r="F9">
-        <v>-0.5663242909476262</v>
+        <v>-0.4440688594380583</v>
       </c>
       <c r="G9">
-        <v>-10.79889145176815</v>
+        <v>-9.898118494896774</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-24.25406353513974</v>
       </c>
       <c r="E10">
-        <v>-22.39113690558785</v>
+        <v>-21.36691382537701</v>
       </c>
       <c r="F10">
-        <v>-0.6107852545580841</v>
+        <v>-0.3646333957140026</v>
       </c>
       <c r="G10">
-        <v>-10.93829521388132</v>
+        <v>-9.950534362420054</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-23.25447109362458</v>
       </c>
       <c r="E11">
-        <v>-22.48472234943036</v>
+        <v>-23.14316247014563</v>
       </c>
       <c r="F11">
-        <v>-0.2809252129263069</v>
+        <v>-0.564284022034531</v>
       </c>
       <c r="G11">
-        <v>-10.24578205579442</v>
+        <v>-9.919703251812823</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-22.15695362131927</v>
       </c>
       <c r="E12">
-        <v>-24.00312421267624</v>
+        <v>-23.17406930524798</v>
       </c>
       <c r="F12">
-        <v>-0.01961091714138325</v>
+        <v>-0.5771908145375501</v>
       </c>
       <c r="G12">
-        <v>-10.50774883486248</v>
+        <v>-9.518739907732915</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.99827976290885</v>
       </c>
       <c r="E13">
-        <v>-24.07951051223762</v>
+        <v>-23.78195807061563</v>
       </c>
       <c r="F13">
-        <v>0.008598306393551115</v>
+        <v>-0.009323422366016187</v>
       </c>
       <c r="G13">
-        <v>-9.906692807843486</v>
+        <v>-8.403158893000388</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.85260788001859</v>
       </c>
       <c r="E14">
-        <v>-24.49120766969696</v>
+        <v>-24.57578145026421</v>
       </c>
       <c r="F14">
-        <v>0.4436245600151423</v>
+        <v>-0.2265387510955053</v>
       </c>
       <c r="G14">
-        <v>-9.256932034850731</v>
+        <v>-9.581544267158428</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.76910495507597</v>
       </c>
       <c r="E15">
-        <v>-26.04691057334402</v>
+        <v>-25.3503044736921</v>
       </c>
       <c r="F15">
-        <v>0.3327086498824969</v>
+        <v>0.1448009598640542</v>
       </c>
       <c r="G15">
-        <v>-9.422982378009495</v>
+        <v>-7.447401085267257</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.7994480290464</v>
       </c>
       <c r="E16">
-        <v>-26.47783110296592</v>
+        <v>-26.70369327257248</v>
       </c>
       <c r="F16">
-        <v>0.8379970266095421</v>
+        <v>0.08389110473620658</v>
       </c>
       <c r="G16">
-        <v>-9.469621343566747</v>
+        <v>-7.628557447721716</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.98769907750216</v>
       </c>
       <c r="E17">
-        <v>-28.06390195330841</v>
+        <v>-26.71964255802749</v>
       </c>
       <c r="F17">
-        <v>1.344407841167381</v>
+        <v>0.5532440751624065</v>
       </c>
       <c r="G17">
-        <v>-9.063083040798707</v>
+        <v>-8.123444279296287</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.35593228602728</v>
       </c>
       <c r="E18">
-        <v>-28.18772401810014</v>
+        <v>-27.58079076074811</v>
       </c>
       <c r="F18">
-        <v>1.444201262182637</v>
+        <v>0.7307234479470062</v>
       </c>
       <c r="G18">
-        <v>-8.197997764840673</v>
+        <v>-7.643746230655892</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.92939428556761</v>
       </c>
       <c r="E19">
-        <v>-28.87708455933979</v>
+        <v>-29.139935304641</v>
       </c>
       <c r="F19">
-        <v>1.733052975538825</v>
+        <v>1.18031157214241</v>
       </c>
       <c r="G19">
-        <v>-7.963611140660274</v>
+        <v>-7.450436855526768</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.69955940759725</v>
       </c>
       <c r="E20">
-        <v>-29.10867977704006</v>
+        <v>-28.79041862378099</v>
       </c>
       <c r="F20">
-        <v>1.815815162752523</v>
+        <v>1.404819019118743</v>
       </c>
       <c r="G20">
-        <v>-7.969152993893014</v>
+        <v>-7.283492665072401</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.66646255116202</v>
       </c>
       <c r="E21">
-        <v>-30.68388681823816</v>
+        <v>-30.0344855316422</v>
       </c>
       <c r="F21">
-        <v>2.115672565422305</v>
+        <v>1.871559318756513</v>
       </c>
       <c r="G21">
-        <v>-7.851128734872457</v>
+        <v>-7.068346931566245</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.79413175933512</v>
       </c>
       <c r="E22">
-        <v>-31.23022909336756</v>
+        <v>-30.29797026330449</v>
       </c>
       <c r="F22">
-        <v>2.133247208240099</v>
+        <v>1.96847664814925</v>
       </c>
       <c r="G22">
-        <v>-7.166067614794453</v>
+        <v>-7.260150008475001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.04671815772069</v>
       </c>
       <c r="E23">
-        <v>-31.43433647384127</v>
+        <v>-30.63648501656287</v>
       </c>
       <c r="F23">
-        <v>2.14084002385416</v>
+        <v>2.084242649425286</v>
       </c>
       <c r="G23">
-        <v>-7.261182898683253</v>
+        <v>-6.843200039985951</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.37842166724804</v>
       </c>
       <c r="E24">
-        <v>-31.53266549420682</v>
+        <v>-31.18216839872415</v>
       </c>
       <c r="F24">
-        <v>2.6390549713287</v>
+        <v>2.175914756423496</v>
       </c>
       <c r="G24">
-        <v>-7.847775152241175</v>
+        <v>-6.873312762211162</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.7339039043724</v>
       </c>
       <c r="E25">
-        <v>-31.84279124391112</v>
+        <v>-31.10776783501513</v>
       </c>
       <c r="F25">
-        <v>2.357693356028626</v>
+        <v>2.463492440714178</v>
       </c>
       <c r="G25">
-        <v>-7.630100161943016</v>
+        <v>-6.62784905265636</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.07090370348143</v>
       </c>
       <c r="E26">
-        <v>-31.69627246739294</v>
+        <v>-31.94476795008984</v>
       </c>
       <c r="F26">
-        <v>2.582883377744865</v>
+        <v>2.383137489173015</v>
       </c>
       <c r="G26">
-        <v>-7.372794630994242</v>
+        <v>-7.46655590175748</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.33864170604571</v>
       </c>
       <c r="E27">
-        <v>-32.5351858627359</v>
+        <v>-31.48893175647775</v>
       </c>
       <c r="F27">
-        <v>2.875341802772842</v>
+        <v>2.189735238171803</v>
       </c>
       <c r="G27">
-        <v>-7.510579536338708</v>
+        <v>-7.386377799341871</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.51005377840077</v>
       </c>
       <c r="E28">
-        <v>-32.39865689987865</v>
+        <v>-31.28158425285154</v>
       </c>
       <c r="F28">
-        <v>2.540267188340442</v>
+        <v>2.375513195597649</v>
       </c>
       <c r="G28">
-        <v>-7.027421967609775</v>
+        <v>-6.966560898415813</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.5547049899691</v>
       </c>
       <c r="E29">
-        <v>-32.74740374015735</v>
+        <v>-31.36796715878486</v>
       </c>
       <c r="F29">
-        <v>2.382658692814197</v>
+        <v>2.555409744463617</v>
       </c>
       <c r="G29">
-        <v>-6.850181980528274</v>
+        <v>-6.749581122680901</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.46790860578347</v>
       </c>
       <c r="E30">
-        <v>-32.12622843205121</v>
+        <v>-29.31783640603233</v>
       </c>
       <c r="F30">
-        <v>2.572455888878425</v>
+        <v>2.164569436474754</v>
       </c>
       <c r="G30">
-        <v>-7.152441409354812</v>
+        <v>-7.470154464758668</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.2505655923777</v>
       </c>
       <c r="E31">
-        <v>-32.37385444773864</v>
+        <v>-30.97876293172162</v>
       </c>
       <c r="F31">
-        <v>2.280088584264757</v>
+        <v>2.270635255464009</v>
       </c>
       <c r="G31">
-        <v>-7.166752897721081</v>
+        <v>-7.541635764042612</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.91139474860451</v>
       </c>
       <c r="E32">
-        <v>-32.40510091839156</v>
+        <v>-31.2803819430025</v>
       </c>
       <c r="F32">
-        <v>2.546975307568312</v>
+        <v>1.935007291606539</v>
       </c>
       <c r="G32">
-        <v>-7.730886410340588</v>
+        <v>-6.651569111445238</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.47503902607576</v>
       </c>
       <c r="E33">
-        <v>-31.72397314289786</v>
+        <v>-30.22398179073017</v>
       </c>
       <c r="F33">
-        <v>2.457110698243011</v>
+        <v>2.086480898147651</v>
       </c>
       <c r="G33">
-        <v>-6.829646666548175</v>
+        <v>-7.498376865480955</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.9605578335938</v>
       </c>
       <c r="E34">
-        <v>-31.09931996675382</v>
+        <v>-30.05976347355301</v>
       </c>
       <c r="F34">
-        <v>2.334861893672666</v>
+        <v>1.957881829067444</v>
       </c>
       <c r="G34">
-        <v>-6.520127211354016</v>
+        <v>-7.220072544176583</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.40176258669047</v>
       </c>
       <c r="E35">
-        <v>-30.58428756091346</v>
+        <v>-30.13260397796639</v>
       </c>
       <c r="F35">
-        <v>2.261196837276511</v>
+        <v>1.811260798771932</v>
       </c>
       <c r="G35">
-        <v>-7.222065492591224</v>
+        <v>-7.79401520322895</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.81762009621385</v>
       </c>
       <c r="E36">
-        <v>-29.7553503938094</v>
+        <v>-29.67593001666287</v>
       </c>
       <c r="F36">
-        <v>1.979513815424151</v>
+        <v>2.002172977360328</v>
       </c>
       <c r="G36">
-        <v>-6.963498643791987</v>
+        <v>-7.553050525062019</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.24269665149348</v>
       </c>
       <c r="E37">
-        <v>-30.00362850975393</v>
+        <v>-29.03381957321926</v>
       </c>
       <c r="F37">
-        <v>2.072148485344413</v>
+        <v>1.739722989866166</v>
       </c>
       <c r="G37">
-        <v>-6.590175044419454</v>
+        <v>-7.519865616576364</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.69423602054057</v>
       </c>
       <c r="E38">
-        <v>-29.57958899638669</v>
+        <v>-29.31395097533375</v>
       </c>
       <c r="F38">
-        <v>2.146433160557862</v>
+        <v>2.085670754827713</v>
       </c>
       <c r="G38">
-        <v>-6.598931437370827</v>
+        <v>-6.547849719699872</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.1926179248</v>
       </c>
       <c r="E39">
-        <v>-29.47711642230412</v>
+        <v>-28.16768099214219</v>
       </c>
       <c r="F39">
-        <v>2.498693085128741</v>
+        <v>1.625153151119772</v>
       </c>
       <c r="G39">
-        <v>-6.342844187180504</v>
+        <v>-7.021092204538689</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.7545637405304</v>
       </c>
       <c r="E40">
-        <v>-29.13695556874395</v>
+        <v>-28.39731085212314</v>
       </c>
       <c r="F40">
-        <v>2.20900306396092</v>
+        <v>1.901527994654994</v>
       </c>
       <c r="G40">
-        <v>-6.853005875873272</v>
+        <v>-6.97107317198584</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.38635389019285</v>
       </c>
       <c r="E41">
-        <v>-28.05732208057526</v>
+        <v>-26.84869501029808</v>
       </c>
       <c r="F41">
-        <v>2.137370821171235</v>
+        <v>1.519165198666381</v>
       </c>
       <c r="G41">
-        <v>-6.431709161091161</v>
+        <v>-6.326182211481352</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.09914541614675</v>
       </c>
       <c r="E42">
-        <v>-28.19057242825097</v>
+        <v>-27.31937554170733</v>
       </c>
       <c r="F42">
-        <v>2.120195451441591</v>
+        <v>1.416928093812866</v>
       </c>
       <c r="G42">
-        <v>-6.166451699757056</v>
+        <v>-6.31351937479364</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.88740748631713</v>
       </c>
       <c r="E43">
-        <v>-27.75692575727645</v>
+        <v>-26.99522737223828</v>
       </c>
       <c r="F43">
-        <v>2.067259460933091</v>
+        <v>1.514372264873783</v>
       </c>
       <c r="G43">
-        <v>-6.31542293847872</v>
+        <v>-7.00782353801729</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.7569802931668</v>
       </c>
       <c r="E44">
-        <v>-27.83374226186857</v>
+        <v>-26.82400124153426</v>
       </c>
       <c r="F44">
-        <v>2.140190583810365</v>
+        <v>1.623841017153738</v>
       </c>
       <c r="G44">
-        <v>-6.531637978194062</v>
+        <v>-6.233092981462586</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.69583652881553</v>
       </c>
       <c r="E45">
-        <v>-27.27580709327953</v>
+        <v>-26.18573547252316</v>
       </c>
       <c r="F45">
-        <v>2.248776296438936</v>
+        <v>1.21695854604226</v>
       </c>
       <c r="G45">
-        <v>-6.258216711560115</v>
+        <v>-7.10443518848984</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.69771291735</v>
       </c>
       <c r="E46">
-        <v>-26.56491818660742</v>
+        <v>-25.49999318201565</v>
       </c>
       <c r="F46">
-        <v>1.971337829158519</v>
+        <v>1.398480351752521</v>
       </c>
       <c r="G46">
-        <v>-6.155755327119671</v>
+        <v>-6.79851098575133</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.75052778407813</v>
       </c>
       <c r="E47">
-        <v>-25.58875127256599</v>
+        <v>-24.17404240714774</v>
       </c>
       <c r="F47">
-        <v>2.212230383362227</v>
+        <v>1.786424687301197</v>
       </c>
       <c r="G47">
-        <v>-5.965501585523295</v>
+        <v>-7.071925631294198</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.83595546434211</v>
       </c>
       <c r="E48">
-        <v>-25.34488841877893</v>
+        <v>-24.19820634445267</v>
       </c>
       <c r="F48">
-        <v>2.272234004551412</v>
+        <v>1.581801371461663</v>
       </c>
       <c r="G48">
-        <v>-6.766640363844766</v>
+        <v>-6.479126104850142</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.94528907089838</v>
       </c>
       <c r="E49">
-        <v>-25.70868790665913</v>
+        <v>-23.8926973739992</v>
       </c>
       <c r="F49">
-        <v>2.040478342800583</v>
+        <v>1.140518458846727</v>
       </c>
       <c r="G49">
-        <v>-6.242130770784796</v>
+        <v>-6.640899223172168</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.06038709804108</v>
       </c>
       <c r="E50">
-        <v>-24.78323084455559</v>
+        <v>-23.5348664148611</v>
       </c>
       <c r="F50">
-        <v>1.750324435887194</v>
+        <v>1.304036527424544</v>
       </c>
       <c r="G50">
-        <v>-6.460279169095071</v>
+        <v>-6.164458751342416</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.17630537024733</v>
       </c>
       <c r="E51">
-        <v>-24.39126877682168</v>
+        <v>-22.76430580618992</v>
       </c>
       <c r="F51">
-        <v>2.024416298860301</v>
+        <v>1.756538848142996</v>
       </c>
       <c r="G51">
-        <v>-6.509328211804913</v>
+        <v>-6.39519053324746</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.27989937164972</v>
       </c>
       <c r="E52">
-        <v>-23.84318303919933</v>
+        <v>-23.32487201817741</v>
       </c>
       <c r="F52">
-        <v>2.016828453450657</v>
+        <v>1.653965426123945</v>
       </c>
       <c r="G52">
-        <v>-6.035460033859175</v>
+        <v>-7.302710381927871</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.37078658200383</v>
       </c>
       <c r="E53">
-        <v>-23.63414415053126</v>
+        <v>-23.03432059737127</v>
       </c>
       <c r="F53">
-        <v>2.097400437251354</v>
+        <v>1.799426742055538</v>
       </c>
       <c r="G53">
-        <v>-6.448069877146239</v>
+        <v>-7.468204553436038</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.44915671931816</v>
       </c>
       <c r="E54">
-        <v>-22.65001165071033</v>
+        <v>-22.49700809941317</v>
       </c>
       <c r="F54">
-        <v>2.127046049862742</v>
+        <v>1.426479169967144</v>
       </c>
       <c r="G54">
-        <v>-6.447560053133191</v>
+        <v>-6.660398336398475</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.51202410420839</v>
       </c>
       <c r="E55">
-        <v>-22.80274349356703</v>
+        <v>-22.07457845855566</v>
       </c>
       <c r="F55">
-        <v>2.407406997340235</v>
+        <v>1.52484614231478</v>
       </c>
       <c r="G55">
-        <v>-6.937994200957442</v>
+        <v>-6.716207513099508</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.57100730135489</v>
       </c>
       <c r="E56">
-        <v>-22.09057302875075</v>
+        <v>-22.43822850679361</v>
       </c>
       <c r="F56">
-        <v>2.313657344895804</v>
+        <v>1.739287268612294</v>
       </c>
       <c r="G56">
-        <v>-7.066910154802201</v>
+        <v>-6.486829744320025</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.62661440293281</v>
       </c>
       <c r="E57">
-        <v>-21.96114924161153</v>
+        <v>-21.03048443439916</v>
       </c>
       <c r="F57">
-        <v>2.284099539229112</v>
+        <v>1.349663003970741</v>
       </c>
       <c r="G57">
-        <v>-7.034973321984853</v>
+        <v>-7.199633236017123</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.69139402239578</v>
       </c>
       <c r="E58">
-        <v>-22.12352220563056</v>
+        <v>-21.22083883931159</v>
       </c>
       <c r="F58">
-        <v>2.128757456916926</v>
+        <v>1.677249177081833</v>
       </c>
       <c r="G58">
-        <v>-7.28672375751873</v>
+        <v>-7.106318888901686</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.76722638044808</v>
       </c>
       <c r="E59">
-        <v>-21.71691958142985</v>
+        <v>-20.756448358299</v>
       </c>
       <c r="F59">
-        <v>2.238229522666492</v>
+        <v>1.746353242558174</v>
       </c>
       <c r="G59">
-        <v>-7.730267338324745</v>
+        <v>-7.266383765725448</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.86361663722014</v>
       </c>
       <c r="E60">
-        <v>-20.89676312542667</v>
+        <v>-21.12581786920864</v>
       </c>
       <c r="F60">
-        <v>2.398288328970218</v>
+        <v>1.419714721755884</v>
       </c>
       <c r="G60">
-        <v>-7.502428973221023</v>
+        <v>-7.084545430889899</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.98461690488475</v>
       </c>
       <c r="E61">
-        <v>-21.7472377149112</v>
+        <v>-20.23704144656723</v>
       </c>
       <c r="F61">
-        <v>2.461113369533338</v>
+        <v>1.709600237630765</v>
       </c>
       <c r="G61">
-        <v>-7.607406372271312</v>
+        <v>-7.509371187216875</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.12977691801231</v>
       </c>
       <c r="E62">
-        <v>-20.85352072712742</v>
+        <v>-20.67241346613866</v>
       </c>
       <c r="F62">
-        <v>2.036285147007612</v>
+        <v>1.633160150435232</v>
       </c>
       <c r="G62">
-        <v>-8.079192217072849</v>
+        <v>-7.908401172701848</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.30433275885646</v>
       </c>
       <c r="E63">
-        <v>-21.35935580225821</v>
+        <v>-20.50471501668661</v>
       </c>
       <c r="F63">
-        <v>2.1377154220108</v>
+        <v>1.539355825742216</v>
       </c>
       <c r="G63">
-        <v>-7.931753760935868</v>
+        <v>-7.926033138244007</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.49870201563649</v>
       </c>
       <c r="E64">
-        <v>-19.59476797805934</v>
+        <v>-20.03956828051474</v>
       </c>
       <c r="F64">
-        <v>2.298095634866812</v>
+        <v>1.18531822472493</v>
       </c>
       <c r="G64">
-        <v>-8.130465946385081</v>
+        <v>-7.583328774564193</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.71377540220802</v>
       </c>
       <c r="E65">
-        <v>-19.43088703219576</v>
+        <v>-18.67018943991328</v>
       </c>
       <c r="F65">
-        <v>2.081050121454897</v>
+        <v>1.594477049459301</v>
       </c>
       <c r="G65">
-        <v>-8.603665394131887</v>
+        <v>-8.533326233058991</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.93637062165762</v>
       </c>
       <c r="E66">
-        <v>-19.91618094922775</v>
+        <v>-19.28834425585632</v>
       </c>
       <c r="F66">
-        <v>2.295176468139347</v>
+        <v>1.360978502692982</v>
       </c>
       <c r="G66">
-        <v>-7.935431777029998</v>
+        <v>-8.401943922787476</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.16196089501867</v>
       </c>
       <c r="E67">
-        <v>-19.06811550791529</v>
+        <v>-20.0515868505311</v>
       </c>
       <c r="F67">
-        <v>2.169595969874942</v>
+        <v>1.425294604581141</v>
       </c>
       <c r="G67">
-        <v>-8.852366817224095</v>
+        <v>-8.30703389272211</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.37688376344034</v>
       </c>
       <c r="E68">
-        <v>-19.33845182075119</v>
+        <v>-19.31234969657098</v>
       </c>
       <c r="F68">
-        <v>1.898227778922241</v>
+        <v>1.320789429778761</v>
       </c>
       <c r="G68">
-        <v>-8.673733090470561</v>
+        <v>-8.065665327999387</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.57211142884497</v>
       </c>
       <c r="E69">
-        <v>-19.39044323083325</v>
+        <v>-18.52987014431161</v>
       </c>
       <c r="F69">
-        <v>1.993047682051089</v>
+        <v>1.243620379268765</v>
       </c>
       <c r="G69">
-        <v>-8.57676059053423</v>
+        <v>-8.175403291535147</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.74096898175444</v>
       </c>
       <c r="E70">
-        <v>-19.79878026057889</v>
+        <v>-20.13523229392678</v>
       </c>
       <c r="F70">
-        <v>2.082176701122704</v>
+        <v>1.437302618452123</v>
       </c>
       <c r="G70">
-        <v>-8.904438388011291</v>
+        <v>-8.006396631209816</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.86886628171977</v>
       </c>
       <c r="E71">
-        <v>-19.34361880959394</v>
+        <v>-19.87681945315308</v>
       </c>
       <c r="F71">
-        <v>1.700501450078415</v>
+        <v>0.9445631795100873</v>
       </c>
       <c r="G71">
-        <v>-8.507222581481839</v>
+        <v>-8.179928807287332</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.95612768104203</v>
       </c>
       <c r="E72">
-        <v>-20.09361108932228</v>
+        <v>-19.62003233454813</v>
       </c>
       <c r="F72">
-        <v>1.7518055568034</v>
+        <v>1.251127044672934</v>
       </c>
       <c r="G72">
-        <v>-8.360012552987067</v>
+        <v>-8.108374676001525</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.99352366145164</v>
       </c>
       <c r="E73">
-        <v>-19.75542917890347</v>
+        <v>-20.03655684529964</v>
       </c>
       <c r="F73">
-        <v>1.681475507570916</v>
+        <v>0.8551508587867143</v>
       </c>
       <c r="G73">
-        <v>-8.650489750239338</v>
+        <v>-7.94891562901145</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.98681785905981</v>
       </c>
       <c r="E74">
-        <v>-19.57039573095006</v>
+        <v>-19.03926912848643</v>
       </c>
       <c r="F74">
-        <v>1.582676127439019</v>
+        <v>0.994003459578773</v>
       </c>
       <c r="G74">
-        <v>-8.109086443292467</v>
+        <v>-8.138477466590118</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.93218878319233</v>
       </c>
       <c r="E75">
-        <v>-20.00517452042649</v>
+        <v>-18.79285221535905</v>
       </c>
       <c r="F75">
-        <v>1.483934733025318</v>
+        <v>1.099156417690142</v>
       </c>
       <c r="G75">
-        <v>-8.382279282284205</v>
+        <v>-9.000586562108344</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.83952252310231</v>
       </c>
       <c r="E76">
-        <v>-19.95756214470984</v>
+        <v>-20.20161066593121</v>
       </c>
       <c r="F76">
-        <v>1.244960677726494</v>
+        <v>0.8977687049259433</v>
       </c>
       <c r="G76">
-        <v>-8.365051203297837</v>
+        <v>-8.323689247330183</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.71312609406988</v>
       </c>
       <c r="E77">
-        <v>-19.64604388924819</v>
+        <v>-19.97048640952773</v>
       </c>
       <c r="F77">
-        <v>1.310318865807375</v>
+        <v>0.6495020241025146</v>
       </c>
       <c r="G77">
-        <v>-7.90675914211437</v>
+        <v>-7.649208630795689</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.55740675828343</v>
       </c>
       <c r="E78">
-        <v>-19.93213929163078</v>
+        <v>-20.67004054575864</v>
       </c>
       <c r="F78">
-        <v>1.365310864209623</v>
+        <v>0.5096553824270965</v>
       </c>
       <c r="G78">
-        <v>-7.794849460704847</v>
+        <v>-7.757105931011615</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.38366048520156</v>
       </c>
       <c r="E79">
-        <v>-20.53208964206298</v>
+        <v>-20.41049558648302</v>
       </c>
       <c r="F79">
-        <v>0.9777856825667642</v>
+        <v>0.3512947292991094</v>
       </c>
       <c r="G79">
-        <v>-7.866797546909828</v>
+        <v>-7.356020096746755</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.1936184924982</v>
       </c>
       <c r="E80">
-        <v>-21.15787040823493</v>
+        <v>-20.35252659071083</v>
       </c>
       <c r="F80">
-        <v>0.9761521420484437</v>
+        <v>0.3554042599843977</v>
       </c>
       <c r="G80">
-        <v>-7.068548874844141</v>
+        <v>-6.926682066849753</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.99856350254017</v>
       </c>
       <c r="E81">
-        <v>-21.48145704692702</v>
+        <v>-21.75933326898569</v>
       </c>
       <c r="F81">
-        <v>0.684028377451198</v>
+        <v>0.3067674962964276</v>
       </c>
       <c r="G81">
-        <v>-7.480264870835602</v>
+        <v>-7.096248209371223</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.79618461055038</v>
       </c>
       <c r="E82">
-        <v>-22.55820589715283</v>
+        <v>-22.39518083287669</v>
       </c>
       <c r="F82">
-        <v>0.9151114048709537</v>
+        <v>0.2525351108025467</v>
       </c>
       <c r="G82">
-        <v>-7.073001558594461</v>
+        <v>-6.938669552247454</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.5957421368711</v>
       </c>
       <c r="E83">
-        <v>-22.8695022573881</v>
+        <v>-21.44060568290383</v>
       </c>
       <c r="F83">
-        <v>0.8492926445141161</v>
+        <v>0.4007954801881994</v>
       </c>
       <c r="G83">
-        <v>-6.548869367725968</v>
+        <v>-6.902409146955816</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.39264626084231</v>
       </c>
       <c r="E84">
-        <v>-23.45858427020189</v>
+        <v>-24.07332914521715</v>
       </c>
       <c r="F84">
-        <v>0.6059216150412327</v>
+        <v>0.2657583396534353</v>
       </c>
       <c r="G84">
-        <v>-6.77216235380427</v>
+        <v>-6.439081746007117</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.18951992840155</v>
       </c>
       <c r="E85">
-        <v>-24.36327827898027</v>
+        <v>-23.81915948458864</v>
       </c>
       <c r="F85">
-        <v>0.707078528801497</v>
+        <v>-0.2285873036826285</v>
       </c>
       <c r="G85">
-        <v>-6.356291623161024</v>
+        <v>-6.417073239262042</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.98480191321957</v>
       </c>
       <c r="E86">
-        <v>-24.85581322595053</v>
+        <v>-25.44215098351567</v>
       </c>
       <c r="F86">
-        <v>0.4198653261680468</v>
+        <v>-0.4356112282554754</v>
       </c>
       <c r="G86">
-        <v>-5.966104104811443</v>
+        <v>-6.547190921137557</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.77306995056501</v>
       </c>
       <c r="E87">
-        <v>-25.73714483732333</v>
+        <v>-27.0742899999382</v>
       </c>
       <c r="F87">
-        <v>0.4191537585690421</v>
+        <v>-0.3237170162201238</v>
       </c>
       <c r="G87">
-        <v>-6.264933808459296</v>
+        <v>-6.766504631477655</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.5555113565009</v>
       </c>
       <c r="E88">
-        <v>-27.13287939664944</v>
+        <v>-26.73379856777547</v>
       </c>
       <c r="F88">
-        <v>0.06013518435872236</v>
+        <v>-0.6153445887430925</v>
       </c>
       <c r="G88">
-        <v>-5.796200286644967</v>
+        <v>-6.212216681291942</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.32373534689747</v>
       </c>
       <c r="E89">
-        <v>-28.1666801993865</v>
+        <v>-29.01537057011202</v>
       </c>
       <c r="F89">
-        <v>-0.08556884322189108</v>
+        <v>-0.5600394674625863</v>
       </c>
       <c r="G89">
-        <v>-5.826846006702</v>
+        <v>-6.148031824376551</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.081901534047</v>
       </c>
       <c r="E90">
-        <v>-29.62572282533983</v>
+        <v>-30.15860194724443</v>
       </c>
       <c r="F90">
-        <v>-0.1601260513108606</v>
+        <v>-0.793353288298081</v>
       </c>
       <c r="G90">
-        <v>-6.039462483416153</v>
+        <v>-5.960896616678169</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.82190001622437</v>
       </c>
       <c r="E91">
-        <v>-31.06624172836479</v>
+        <v>-30.73477554489935</v>
       </c>
       <c r="F91">
-        <v>-0.3821997548577689</v>
+        <v>-1.097359983288486</v>
       </c>
       <c r="G91">
-        <v>-5.705425127958151</v>
+        <v>-5.609118047675213</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.55223553289293</v>
       </c>
       <c r="E92">
-        <v>-32.33336083316205</v>
+        <v>-33.92591645828352</v>
       </c>
       <c r="F92">
-        <v>-0.6582415946970649</v>
+        <v>-1.074244390913365</v>
       </c>
       <c r="G92">
-        <v>-5.582299318261577</v>
+        <v>-6.351987913959971</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.2756708370078</v>
       </c>
       <c r="E93">
-        <v>-33.62525069078126</v>
+        <v>-33.76016298841778</v>
       </c>
       <c r="F93">
-        <v>-0.688893673702855</v>
+        <v>-1.329760943246095</v>
       </c>
       <c r="G93">
-        <v>-5.503336186058881</v>
+        <v>-6.005824030191619</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.99791823605071</v>
       </c>
       <c r="E94">
-        <v>-35.40541646556651</v>
+        <v>-35.67760266003454</v>
       </c>
       <c r="F94">
-        <v>-0.8959374790933691</v>
+        <v>-1.666176684503628</v>
       </c>
       <c r="G94">
-        <v>-5.473660455844854</v>
+        <v>-6.561025690946171</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.7316001391709</v>
       </c>
       <c r="E95">
-        <v>-38.11491114773187</v>
+        <v>-37.06442744675056</v>
       </c>
       <c r="F95">
-        <v>-0.9775821986806911</v>
+        <v>-1.826062362020169</v>
       </c>
       <c r="G95">
-        <v>-5.494609588017362</v>
+        <v>-6.147598142910907</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.48590981350868</v>
       </c>
       <c r="E96">
-        <v>-39.50691650871266</v>
+        <v>-39.92015561157161</v>
       </c>
       <c r="F96">
-        <v>-1.301106886415858</v>
+        <v>-2.14908257400703</v>
       </c>
       <c r="G96">
-        <v>-5.582296007716038</v>
+        <v>-6.804582526270353</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.27418727771712</v>
       </c>
       <c r="E97">
-        <v>-41.67828130336153</v>
+        <v>-41.03128237222664</v>
       </c>
       <c r="F97">
-        <v>-1.588892490924642</v>
+        <v>-2.059827643090189</v>
       </c>
       <c r="G97">
-        <v>-6.576906377898055</v>
+        <v>-6.097973065277232</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.1078410639852</v>
       </c>
       <c r="E98">
-        <v>-43.46865199432307</v>
+        <v>-43.3880791205416</v>
       </c>
       <c r="F98">
-        <v>-1.659737784681667</v>
+        <v>-2.390661016420256</v>
       </c>
       <c r="G98">
-        <v>-6.098631863839547</v>
+        <v>-6.466651969258168</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.99243596267852</v>
       </c>
       <c r="E99">
-        <v>-45.46302591085615</v>
+        <v>-45.25563991520088</v>
       </c>
       <c r="F99">
-        <v>-1.967272496440595</v>
+        <v>-2.540441439990046</v>
       </c>
       <c r="G99">
-        <v>-6.832718852808618</v>
+        <v>-7.080387385692575</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.946517114478986</v>
       </c>
       <c r="E100">
-        <v>-48.36181307077914</v>
+        <v>-47.79097175126824</v>
       </c>
       <c r="F100">
-        <v>-2.113618508758378</v>
+        <v>-3.002125385001128</v>
       </c>
       <c r="G100">
-        <v>-6.684989068664181</v>
+        <v>-7.553749050170804</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.948078450308246</v>
       </c>
       <c r="E101">
-        <v>-49.63849744479909</v>
+        <v>-49.2794313443754</v>
       </c>
       <c r="F101">
-        <v>-2.053142718149597</v>
+        <v>-3.049898989855381</v>
       </c>
       <c r="G101">
-        <v>-7.084446114523721</v>
+        <v>-7.585232338249273</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.04111139068614</v>
       </c>
       <c r="E102">
-        <v>-52.39041373934981</v>
+        <v>-52.69065609453236</v>
       </c>
       <c r="F102">
-        <v>-2.260262733341169</v>
+        <v>-3.228957230909716</v>
       </c>
       <c r="G102">
-        <v>-7.742344208452006</v>
+        <v>-7.724132897440475</v>
       </c>
     </row>
   </sheetData>
